--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Issued 2026-10-11 for review and approval</t>
+          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -904,10 +904,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -922,10 +926,14 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -940,10 +948,14 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -954,44 +966,92 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
+          <t>Approval record</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>First issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-003</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025 plan vs actual'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered 2026'!$A$4:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Forward plan'!$A$4:$F$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Milestones'!$A$4:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Milestones'!$A$4:$D$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +56,17 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -127,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,6 +168,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -534,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -619,7 +634,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -633,7 +648,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -675,7 +690,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
+          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -807,7 +822,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>The 2026 increments and releases, dated by commits</t>
+          <t>The six 2026 versions v1.0.0 → v1.4.1, dated by commits</t>
         </is>
       </c>
       <c r="C21" s="2" t="n"/>
@@ -887,7 +902,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -904,14 +919,10 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Alexander Peter</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -926,14 +937,10 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -948,14 +955,10 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Anita Johan</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -976,7 +979,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -1052,6 +1055,28 @@
       <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Approved — AR-2026-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1952,6 +1977,63 @@
       <c r="Z25" s="14" t="n"/>
       <c r="AA25" s="14" t="n"/>
     </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Versions (v1.0.0–v1.3.0 retrospective baselines; v1.4.x releases)</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>1.4.0</t>
+        </is>
+      </c>
+      <c r="S26" s="16" t="inlineStr">
+        <is>
+          <t>1.4.1</t>
+        </is>
+      </c>
+      <c r="T26" s="12" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="12" t="n"/>
+      <c r="Y26" s="12" t="n"/>
+      <c r="Z26" s="12" t="n"/>
+      <c r="AA26" s="12" t="n"/>
+    </row>
   </sheetData>
   <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1998,27 +2080,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Planned for</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2025 roadmap item</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>What happened</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
@@ -2035,7 +2117,7 @@
           <t>Enterprise White — baseline secure deployment</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
@@ -2062,7 +2144,7 @@
           <t>Developer White — SDK and test environment</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Not pursued</t>
         </is>
@@ -2089,7 +2171,7 @@
           <t>Personal White — productivity apps</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -2116,7 +2198,7 @@
           <t>Security framework alignment with AJACE standards</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Delivered (2026)</t>
         </is>
@@ -2143,7 +2225,7 @@
           <t>Enterprise Silver — role-based access, performance tuning</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Delivered (2026)</t>
         </is>
@@ -2170,7 +2252,7 @@
           <t>Developer Silver — extended APIs, plug-in marketplace</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2197,7 +2279,7 @@
           <t>Personal Silver — smart assistant with offline mode</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Delivered (2026)</t>
         </is>
@@ -2224,7 +2306,7 @@
           <t>Hardware optimisation for the appliance</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Delivered (2026)</t>
         </is>
@@ -2251,7 +2333,7 @@
           <t>Enterprise Black — compliance suite (GDPR, HIPAA)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Not achieved</t>
         </is>
@@ -2278,7 +2360,7 @@
           <t>Developer Black — cloud-to-edge pipeline</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Not pursued</t>
         </is>
@@ -2305,7 +2387,7 @@
           <t>Personal Black — multi-device sync</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Not pursued</t>
         </is>
@@ -2332,7 +2414,7 @@
           <t>Pilot programmes with partners</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
@@ -2359,7 +2441,7 @@
           <t>White/Silver/Black editions rolled out</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -2386,7 +2468,7 @@
           <t>Analytics dashboard (Enterprise)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2413,7 +2495,7 @@
           <t>Improvements from lessons-learnt logs</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
@@ -2440,7 +2522,7 @@
           <t>High availability and disaster recovery</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2467,7 +2549,7 @@
           <t>Refine the product vision with AJACE leadership</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
@@ -2494,7 +2576,7 @@
           <t>Green AI — energy-efficient models</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2535,70 +2617,70 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Delivered in 2026 — increments and releases</t>
+          <t>Delivered in 2026 — versions v1.0.0 → v1.4.1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Dates are the first and last commit of each increment on main.</t>
+          <t>v1.0.0–v1.3.0: retrospective baselines on the last commit of each two-month increment (REG-08 §2a). v1.4.0, v1.4.1: releases with release records.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Increment / release</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Commit dates</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Key commits</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>Reviews</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Version date</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Version reviews</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Increment 2026-1</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2608,34 +2690,34 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Platform decision; 2025 code ported to the DGX Spark; Kyutai voice; barge-in; wake word and listen-only</t>
+          <t>2025 code ported to the DGX Spark; knowledge chat with citations; live transcription; Kyutai speech; voice with barge-in; wake word and listen-only</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05 → 02-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>4b90b36, c751d79, bff6cf2, 65e01ec, e0ca515</t>
+          <t>595b24b</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>CR-2026-01</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>Delivered</t>
+          <t>CR-2026-01, CR-2026-02, CR-2026-03</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Retrospective baseline — tagged 2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Increment 2026-2</t>
+          <t>v1.1.0</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2645,34 +2727,34 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DoD FMR knowledge base (section and TOC retrieval); financial assistant; TensorRT-LLM integrated; own dual-loop voice; Nemotron speech; field hotspot</t>
+          <t>DoD FMR knowledge base (section and TOC retrieval); financial assistant; TensorRT-LLM integrated; own dual-loop voice; Nemotron speech; personas; offline preparation</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>2026-03-03 → 04-29</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>18715c7, cfe3360, 95d3512, 06e788a, ddc0aa3, d89aeda</t>
+          <t>e5292f3</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>CR-2026-02…06</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Delivered</t>
+          <t>CR-2026-04, CR-2026-05, CR-2026-06, CR-2026-07</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Retrospective baseline — tagged 2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Increment 2026-3</t>
+          <t>v1.2.0</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2682,34 +2764,34 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Silent Assistant; Boardroom with diarisation; code audit; Document Studio; Parakeet final STT; login, roles, tenancy, export gateway; vertical packs; public reference instance</t>
+          <t>Silent Assistant; Boardroom; code-audit fixes; Document Studio; Parakeet final STT; login, roles, tenancy, export gateway; vertical packs; public reference instance</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11 → 06-27</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ec9b180, f540976, b08cf25, 2d23f40, b6a70d8, c9bad3d, d19177d, 7c521f3</t>
+          <t>46bd774</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>CR-2026-07…09; SR-2026-01</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>Delivered</t>
+          <t>CR-2026-08, SR-2026-01, CR-2026-09</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Retrospective baseline — tagged 2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Increment 2026-4</t>
+          <t>v1.3.0</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -2719,17 +2801,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TensorRT-LLM NVFP4 in production; golden evaluation; RAG overhaul; Silent Assistant v2; QASC 2026 paper</t>
+          <t>TensorRT-LLM NVFP4 in production; golden evaluation; retrieval fixes; RAG ingestion overhaul; Silent Assistant v2; QASC 2026 results</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16 → 08-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>80375c6, 12f7219, 7e582e1, 7f2658a, cbc57d1</t>
+          <t>bc9aa33</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2737,9 +2819,9 @@
           <t>RV-2026-01, RV-2026-02</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>Delivered</t>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Retrospective baseline — tagged 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2761,22 +2843,22 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21 → 09-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ff29843, 51fd3bc, eaa7b1a</t>
+          <t>eaa7b1a</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>RV-2026-03…05</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>Released 2026-09-22</t>
+          <t>RV-2026-03, RV-2026-04, RV-2026-05, RV-2026-06</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Release (FRM-03) — tagged on the day</t>
         </is>
       </c>
     </row>
@@ -2798,22 +2880,22 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06 → 10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>e0ed4d0, 3feb5db, f1b8445</t>
+          <t>f1b8445</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>RV-2026-06…08</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>Released 2026-10-06</t>
+          <t>RV-2026-07, RV-2026-08</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Release (FRM-03) — tagged on the day</t>
         </is>
       </c>
     </row>
@@ -2858,32 +2940,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2910,7 +2992,7 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -2942,7 +3024,7 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -2974,7 +3056,7 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3006,7 +3088,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3038,7 +3120,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3070,7 +3152,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3102,7 +3184,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3134,7 +3216,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3166,7 +3248,7 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3198,7 +3280,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3230,7 +3312,7 @@
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3262,7 +3344,7 @@
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3294,7 +3376,7 @@
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3326,7 +3408,7 @@
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3358,7 +3440,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3390,7 +3472,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3422,7 +3504,7 @@
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3454,7 +3536,7 @@
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -3486,7 +3568,7 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3518,7 +3600,7 @@
           <t>2027-Q1</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3550,7 +3632,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3582,7 +3664,7 @@
           <t>2027-H1</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3614,7 +3696,7 @@
           <t>2027-H1</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3646,7 +3728,7 @@
           <t>2027-H1</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
@@ -3679,7 +3761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3696,22 +3778,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3733,7 +3815,7 @@
           <t>DR-2025-01</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3755,7 +3837,7 @@
           <t>DR-2025-09</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3777,7 +3859,7 @@
           <t>DR-2025-13</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3799,7 +3881,7 @@
           <t>DR-2025-14</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3821,7 +3903,7 @@
           <t>DR-2025-15</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3843,7 +3925,7 @@
           <t>CR-2026-01</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3865,7 +3947,7 @@
           <t>4b90b36</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3874,20 +3956,20 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Own dual-loop voice architecture</t>
+          <t>v1.0.0 baseline (retrospective)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ddc0aa3</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+          <t>595b24b</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3896,20 +3978,20 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Security and vertical packs</t>
+          <t>Own dual-loop voice architecture</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>c9bad3d…f75121b</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
+          <t>ddc0aa3</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3918,20 +4000,20 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>TensorRT-LLM NVFP4 in production; golden evaluation</t>
+          <t>v1.1.0 baseline (retrospective)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>80375c6, 12f7219</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+          <t>e5292f3</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3940,20 +4022,20 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>QASC 2026 paper results frozen</t>
+          <t>v1.2.0 baseline (retrospective)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>cbc57d1</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
+          <t>46bd774</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3962,20 +4044,20 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Release v1.4.0</t>
+          <t>v1.3.0 baseline (retrospective)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>eaa7b1a</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+          <t>bc9aa33</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3984,20 +4066,20 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Release v1.4.1</t>
+          <t>Security and vertical packs</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>f1b8445</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
+          <t>c9bad3d…f75121b</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4006,20 +4088,20 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>QMS documents approved</t>
+          <t>TensorRT-LLM NVFP4 in production; golden evaluation</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AR-2026-001</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+          <t>80375c6, 12f7219</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4028,49 +4110,137 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ISO 9001 surveillance audit</t>
+          <t>QASC 2026 paper results frozen</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AUDIT_PACK</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>cbc57d1</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Release v1.4.0</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>eaa7b1a</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Release v1.4.1</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>f1b8445</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>QMS documents approved</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>AR-2026-001</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001 surveillance audit</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>AUDIT_PACK</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>2026-11 → 2027-01</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Internal audits</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>SOP-13</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D20"/>
+  <autoFilter ref="A4:D24"/>
   <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-22_Product_Roadmap.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
+          <t>APPROVED — rev 1.1 2026-10-12 (AR-2026-004); rev 1.0 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -919,10 +919,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -937,10 +941,14 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -955,10 +963,14 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -979,7 +991,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.1: docs/qms/records/approvals/2026-10-12_AR-2026-004_register_revision_approval.md; rev 1.0: …/2026-10-12_AR-2026-003_register_approval.md. Review and approval confirmed by each role holder; signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -1077,6 +1089,28 @@
       <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-004</t>
         </is>
       </c>
     </row>
